--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-condition-diagnosis.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-condition-diagnosis.xlsx
@@ -1118,7 +1118,7 @@
     <t>Condition.code.coding:icd10.system</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ConditionDiseaseCodeICD10_CS</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/CodeSystem/ICD10-2013-full</t>
   </si>
   <si>
     <t>Condition.code.coding:icd10.version</t>
